--- a/data_extactor/batch_10_fa/trimmed/batch_0045_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0045_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال | علوم تجربی | استراتژی‌های یادگیری | نگارش | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | علوم | راهبردهای یادگیری | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | شیمی | آموزش و تدریس | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | شیمی | آموزش و پرورش | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | پرستاران مراقبت‌های ویژه (ICU/CCU) | بهیاران و کمک‌پرستاران دارای مجوز | متخصصان تنفس‌درمانی | کارشناسان اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | پرستاران مراقبت‌های ویژه | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>پرستار-ماماها (Nurse Midwives)</t>
+          <t>ماماهای پرستار (Nurse Midwives)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روان‌شناسی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | درمان و مشاوره | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | خدمات مشتری و شخصی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | کارشناسان پرستاری</t>
+          <t>پرستاران مراقبت‌های حاد | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | پرستاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم تجربی | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران بالینی متخصص | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | دستیاران پزشک | کارشناسان پرستاری</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | ماماهای پرستار | دستیاران پزشک | پرستاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | رایانه و الکترونیک | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان ارزیابی و تجویز سمعک | متخصصان مغز و اعصاب (نورولوژیست) | کاردرمانگران | بینایی‌سنج‌ها (اپتومتریست) | پزشکان متخصص کودکان | گفتاردرمانگران</t>
+          <t>کارشناسان تجویز و ساخت سمعک | متخصصان مغز و اعصاب | کاردرمانگران | بینایی‌سنج‌ها (اپتومتریست‌ها) | متخصصان عمومی کودکان | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | علوم تجربی | نگارش | درک مطلب | سخن گفتن | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | علوم | نگارش | درک مطلب | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | درک کتبی | دید نزدیک | بیان شفاهی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | درک کتبی | بینایی نزدیک | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | پزشکان طب اورژانس | پرستاران بیهوشی | جراحان اطفال | متخصصان تنفس‌درمانی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | پزشکان طب اورژانس | پرستاران بیهوشی | جراحان اطفال | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Epic Systems | MEDITECH software | نرم‌افزار مانیتورینگ Watchman Monitoring</t>
+          <t>Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار مانیتورینگ Watchman Monitoring</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | تکنسین‌ها و کارشناسان قلب و عروق | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژیست) | متخصصان رادیولوژی</t>
+          <t>پرستاران مراقبت‌های حاد | کارشناسان و تکنسین‌های قلب و عروق | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | علوم تجربی | نگارش | نظارت | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | علوم | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | آموزش و تدریس | زیست‌شناسی | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش | زیست‌شناسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | دید نزدیک</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان ایمونولوژی و آلرژی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پرستاران بالینی پیشرفته (NP) | جراحان دهان، فک و صورت | دستیاران پزشک | متخصصان طب پا (پودیاتریست)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پرستاران بالینی پیشرفته | جراحان دهان، فک و صورت | دستیاران پزشک | پزشکان متخصص پا و مچ پا</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Epic Systems | MEDITECH software</t>
+          <t>Epic Systems | نرم‌افزار MEDITECH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران مراقبت‌های ویژه (ICU/CCU) | تکنسین‌های فوریت‌های پزشکی (EMT) | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان (هسپیتالیست) | امدادگران اورژانس (پارامدیک) | دستیاران پزشک</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | دستیاران پزشک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم تجربی | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان (هسپیتالیست) | ماماها | پزشکان متخصص کودکان | دستیاران پزشک | متخصصان طب پیشگیری</t>
+          <t>پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | ماماهای پرستار | متخصصان عمومی کودکان | دستیاران پزشک | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>پزشک | فوق‌تخصص گوارش و کبد | پزشک متخصص بیماری‌های داخلی | متخصص داخلی عمومی | دکترای تخصصی بیماری‌های داخلی | پزشک داخلی | متخصص داخلی (اینترنیست) | دکترای حرفه‌ای پزشکی (MD) | پزشک | پزشک مراقبت‌های اولیه بزرگسالان</t>
+          <t>پزشک | فوق‌تخصص گوارش و کبد | پزشک متخصص بیماری‌های داخلی | متخصص داخلی عمومی | دکترای تخصصی بیماری‌های داخلی | پزشک داخلی | متخصص داخلی (اینترنیست) | دکترای حرفه‌ای پزشکی (MD) | پزشک مراقبت‌های اولیه بزرگسالان</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | علوم تجربی | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | علوم | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | درمان و مشاوره | روان‌شناسی | آموزش و تدریس | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان (هسپیتالیست) | متخصصان مغز و اعصاب (نورولوژیست) | دستیاران پزشک | متخصصان اورولوژی</t>
+          <t>متخصصان بیماری‌های قلب و عروق | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان | متخصصان مغز و اعصاب | دستیاران پزشک | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
